--- a/data/trans_bre/P1805_2016_2023-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P1805_2016_2023-Clase-trans_bre.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,98</t>
+          <t>1,46</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>36,71%</t>
         </is>
       </c>
     </row>
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 4,93</t>
+          <t>-0,45; 4,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 3,51</t>
+          <t>-1,47; 4,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,72; 341,53</t>
+          <t>-25,91; 333,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-42,06; 122,68</t>
+          <t>-26,78; 162,07</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>72,22%</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 2,99</t>
+          <t>-1,78; 2,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 5,36</t>
+          <t>0,17; 5,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-65,08; 407,79</t>
+          <t>-69,82; 250,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,67; 218,19</t>
+          <t>-0,66; 242,79</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2,19</t>
+          <t>1,05</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>110,04%</t>
+          <t>36,77%</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,63; 9,99</t>
+          <t>0,5; 9,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 6,12</t>
+          <t>-1,41; 4,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,84; 547,96</t>
+          <t>-5,1; 611,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-15,26; 761,31</t>
+          <t>-41,82; 302,94</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,33</t>
+          <t>1,24</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>39,82%</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,46; 4,73</t>
+          <t>1,36; 4,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 1,99</t>
+          <t>-0,36; 2,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60,62; 529,19</t>
+          <t>63,05; 531,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-50,9; 87,88</t>
+          <t>-10,88; 121,57</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,9</t>
+          <t>1,31</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>67,58%</t>
         </is>
       </c>
     </row>
@@ -841,29 +841,29 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,35; 4,0</t>
+          <t>0,25; 3,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 2,56</t>
+          <t>-0,24; 2,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,72; 385,9</t>
+          <t>-1,52; 399,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-37,32; 206,05</t>
+          <t>-9,62; 302,0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-2,2</t>
+          <t>-2,87</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-40,84%</t>
+          <t>-48,18%</t>
         </is>
       </c>
     </row>
@@ -901,22 +901,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 2,64</t>
+          <t>-1,67; 2,56</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-9,61; 1,33</t>
+          <t>-9,8; 0,63</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-36,48; 246,16</t>
+          <t>-41,61; 230,8</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-80,76; 70,8</t>
+          <t>-80,96; 26,01</t>
         </is>
       </c>
     </row>
@@ -938,7 +938,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,69</t>
+          <t>0,85</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>25,92%</t>
         </is>
       </c>
     </row>
@@ -961,22 +961,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,08; 2,8</t>
+          <t>1,09; 2,66</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 1,72</t>
+          <t>-0,0; 1,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>49,62; 192,5</t>
+          <t>49,39; 179,65</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-12,67; 69,38</t>
+          <t>-0,3; 65,21</t>
         </is>
       </c>
     </row>
